--- a/painel/planilhas/Valvic_Custo_por_Projeto.xlsx
+++ b/painel/planilhas/Valvic_Custo_por_Projeto.xlsx
@@ -14,7 +14,13 @@
     <sheet name="Listas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instruções'!$A$1:$F$66</definedName>
+    <definedName name="CATEGORIA_COMPRA">Listas!$D$2:$D$17</definedName>
+    <definedName name="FORMA_PAGAMENTO">Listas!$E$2:$E$9</definedName>
+    <definedName name="STATUS_COMPRA">Listas!$F$2:$F$4</definedName>
+    <definedName name="EQUIPE_COMISSAO">Listas!$A$2:$A$9</definedName>
+    <definedName name="VENDEDOR">Listas!$B$2:$B$6</definedName>
+    <definedName name="CAUSA_RETRABALHO">Listas!$C$2:$C$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instruções'!$A$1:$F$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Painel Geral'!$A$1:$R$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Ficha Modelo'!$A$1:$J$182</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Exemplo P-2026-041'!$A$1:$J$182</definedName>
@@ -393,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -649,6 +655,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1369,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1577,240 +1584,245 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Categoria, Forma de pagamento e Status são MENUS SUSPENSOS: clique na célula e escolha. Digitar por fora é permitido, mas a planilha avisa — e o que não estiver escrito igual à lista não entra na soma da categoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Lançamento com valor e sem categoria fica destacado em vermelho, e o total do livro avisa quantos estão sem classificar.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  A CASCATA DE CÁLCULO — A ORDEM IMPORTA</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="4" customHeight="1"/>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="4" customHeight="1"/>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   Valor de venda  −  custos de venda (impostos, máquina, taxas, comissão de venda, projeto, RT)  =  RECEITA LÍQUIDA</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   A receita líquida é a base das comissões de coordenação, produção e montagem. Não é o valor de venda. O marceneiro não deve ser comissionado sobre o imposto nem sobre o RT do arquiteto.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   O RT tem base própria: incide sobre a venda menos impostos, máquina e taxas de transação — como você pediu.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   Depois da receita líquida saem, na ordem: comissões, material, terceirizados, logística e retrabalho. O que sobra é a MARGEM DE CONTRIBUIÇÃO.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="8" customHeight="1"/>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  COMO FUNCIONAM AS COMISSÕES POR AMBIENTE</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-    </row>
-    <row r="39" ht="4" customHeight="1"/>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cada ambiente tem um valor em reais. A planilha calcula o peso dele no projeto e aplica esse peso sobre a receita líquida — essa é a base do ambiente.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="4" customHeight="1"/>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Sobre a base do ambiente incidem dois percentuais: o de quem produziu e o de quem montou. Pessoas diferentes em ambientes diferentes, cada uma com seu percentual.</t>
+          <t xml:space="preserve">   Cada ambiente tem um valor em reais. A planilha calcula o peso dele no projeto e aplica esse peso sobre a receita líquida — essa é a base do ambiente.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exemplo: projeto de R$ 90.000 com cozinha R$ 30.000 (33,3%). Se a receita líquida for R$ 76.000, a base da cozinha é R$ 25.333. A 3% de produção, o Jackson recebe R$ 760 por aquele ambiente.</t>
+          <t xml:space="preserve">   Sobre a base do ambiente incidem dois percentuais: o de quem produziu e o de quem montou. Pessoas diferentes em ambientes diferentes, cada uma com seu percentual.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Exemplo: projeto de R$ 90.000 com cozinha R$ 30.000 (33,3%). Se a receita líquida for R$ 76.000, a base da cozinha é R$ 25.333. A 3% de produção, o Jackson recebe R$ 760 por aquele ambiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">   A tabela "Comissões por colaborador" soma tudo sozinha. Ela lista só marceneiros, ajudantes e o coordenador — quem não recebe comissão não aparece.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   A soma dos ambientes precisa fechar com o valor de venda. A linha de total avisa quando não fecha.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="8" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  RETRABALHO — A PARTE QUE MAIS ENSINA</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-    </row>
-    <row r="47" ht="4" customHeight="1"/>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Registre o que aconteceu, a causa (menu suspenso) e o custo estimado. Não precisa ser exato: o valor aproximado já serve.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="4" customHeight="1"/>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No orçamento você lança a CONTINGÊNCIA prevista. O desvio entre ela e o retrabalho real diz se a sua provisão está no tamanho certo.</t>
+          <t xml:space="preserve">   Registre o que aconteceu, a causa (menu suspenso) e o custo estimado. Não precisa ser exato: o valor aproximado já serve.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">   No orçamento você lança a CONTINGÊNCIA prevista. O desvio entre ela e o retrabalho real diz se a sua provisão está no tamanho certo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Com o tempo, a coluna Causa vira o dado mais valioso da planilha: se metade dos retrabalhos é "erro de medição", o problema não é preço, é processo.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="8" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  O PAINEL GERAL</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n"/>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
-    </row>
-    <row r="53" ht="4" customHeight="1"/>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="4" customHeight="1"/>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sete indicadores no topo: projetos, vendido, custo total, ainda a comprar, margem em reais, margem média e percentual de entrega no prazo.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   A tabela de projetos puxa cada ficha pelo nome da aba. Nome errado deixa a linha em branco — não quebra.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   O bloco "Onde o orçamento erra" soma todos os projetos por categoria e mostra em qual delas você mais estoura. É o retorno direto para ajustar a base de orçamento.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   Dois gráficos: margem por projeto e desvio do orçamento por categoria.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="8" customHeight="1"/>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  CUIDADOS</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
-    </row>
-    <row r="60" ht="4" customHeight="1"/>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+    </row>
+    <row r="61" ht="4" customHeight="1"/>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   A regra de ouro: pode inserir e apagar linhas em qualquer bloco A PARTIR DA LINHA 26. Tudo o que o Painel Geral lê está entre as linhas 6 e 24.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">   Não mexa nas linhas 1 a 25 da ficha. Se elas mudarem de lugar, o Painel passa a ler a célula errada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   A margem calculada aqui é de CONTRIBUIÇÃO: ela ainda não paga o custo fixo da empresa. Um projeto com 30% de MC não deu 30% de lucro.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">   A margem calculada aqui é de CONTRIBUIÇÃO: ela ainda não paga o custo fixo da empresa. Um projeto com 30% de MC não deu 30% de lucro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">   O custo de retrabalho é estimado por você. Não sai de nota fiscal — é a sua leitura do prejuízo, e vale mais registrada por alto do que não registrada.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="8" customHeight="1"/>
-    <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   Abas:   Instruções  ·  Painel Geral  ·  Ficha Modelo (duplique esta)  ·  Exemplo P-2026-041 (preenchido)  ·  Listas</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="50">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A50:F50"/>
@@ -1820,9 +1832,10 @@
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
@@ -1830,29 +1843,31 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A65:F65"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -9536,7 +9551,7 @@
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="36" t="inlineStr">
         <is>
-          <t>MDF / MDP (chapas)</t>
+          <t>MDF e MDP</t>
         </is>
       </c>
       <c r="B82" s="37" t="n"/>
@@ -9592,7 +9607,7 @@
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="36" t="inlineStr">
         <is>
-          <t>Ferragens e acessórios</t>
+          <t>Ferragens</t>
         </is>
       </c>
       <c r="B84" s="37" t="n"/>
@@ -9704,7 +9719,7 @@
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="36" t="inlineStr">
         <is>
-          <t>Consumíveis (parafuso, adesivo, tíner, estopa)</t>
+          <t>Consumíveis</t>
         </is>
       </c>
       <c r="B88" s="37" t="n"/>
@@ -9763,7 +9778,7 @@
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="36" t="inlineStr">
         <is>
-          <t>Acabamento (pintura / laca)</t>
+          <t>Acabamento</t>
         </is>
       </c>
       <c r="B90" s="37" t="n"/>
@@ -9906,7 +9921,7 @@
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="36" t="inlineStr">
         <is>
-          <t>Uber / aplicativo</t>
+          <t>Uber e aplicativo</t>
         </is>
       </c>
       <c r="B95" s="37" t="n"/>
@@ -9934,7 +9949,7 @@
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="36" t="inlineStr">
         <is>
-          <t>Carreto e frete de entrega</t>
+          <t>Carreto e entrega</t>
         </is>
       </c>
       <c r="B96" s="37" t="n"/>
@@ -9962,7 +9977,7 @@
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="36" t="inlineStr">
         <is>
-          <t>Logística da equipe (deslocamento)</t>
+          <t>Deslocamento da equipe</t>
         </is>
       </c>
       <c r="B97" s="37" t="n"/>
@@ -10018,7 +10033,7 @@
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="36" t="inlineStr">
         <is>
-          <t>Estacionamento, pedágio e outros</t>
+          <t>Estacionamento e pedágio</t>
         </is>
       </c>
       <c r="B99" s="37" t="n"/>
@@ -11644,32 +11659,32 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation sqref="D43:D54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="D43:D54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
-    <dataValidation sqref="G43:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="G43:G54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
-    <dataValidation sqref="A66:A77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="A66:A77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
-    <dataValidation sqref="B104:B115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$C$2:$C$10</formula1>
+    <dataValidation sqref="B104:B115" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=CAUSA_RETRABALHO</formula1>
     </dataValidation>
-    <dataValidation sqref="B120:B179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$D$2:$D$17</formula1>
+    <dataValidation sqref="B120:B179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=CATEGORIA_COMPRA</formula1>
     </dataValidation>
-    <dataValidation sqref="G120:G179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$E$2:$E$9</formula1>
+    <dataValidation sqref="G120:G179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=FORMA_PAGAMENTO</formula1>
     </dataValidation>
-    <dataValidation sqref="I120:I179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$F$2:$F$4</formula1>
+    <dataValidation sqref="I120:I179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=STATUS_COMPRA</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:E7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$B$2:$B$6</formula1>
+    <dataValidation sqref="D7:E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=VENDEDOR</formula1>
     </dataValidation>
-    <dataValidation sqref="F9:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="F9:G9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.3" top="0.4" bottom="0.3" header="0.5" footer="0.5"/>
@@ -13769,7 +13784,7 @@
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="36" t="inlineStr">
         <is>
-          <t>MDF / MDP (chapas)</t>
+          <t>MDF e MDP</t>
         </is>
       </c>
       <c r="B82" s="37" t="n"/>
@@ -13829,7 +13844,7 @@
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="36" t="inlineStr">
         <is>
-          <t>Ferragens e acessórios</t>
+          <t>Ferragens</t>
         </is>
       </c>
       <c r="B84" s="37" t="n"/>
@@ -13947,7 +13962,7 @@
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="36" t="inlineStr">
         <is>
-          <t>Consumíveis (parafuso, adesivo, tíner, estopa)</t>
+          <t>Consumíveis</t>
         </is>
       </c>
       <c r="B88" s="37" t="n"/>
@@ -14008,7 +14023,7 @@
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="36" t="inlineStr">
         <is>
-          <t>Acabamento (pintura / laca)</t>
+          <t>Acabamento</t>
         </is>
       </c>
       <c r="B90" s="37" t="n"/>
@@ -14157,7 +14172,7 @@
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="36" t="inlineStr">
         <is>
-          <t>Uber / aplicativo</t>
+          <t>Uber e aplicativo</t>
         </is>
       </c>
       <c r="B95" s="37" t="n"/>
@@ -14187,7 +14202,7 @@
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="36" t="inlineStr">
         <is>
-          <t>Carreto e frete de entrega</t>
+          <t>Carreto e entrega</t>
         </is>
       </c>
       <c r="B96" s="37" t="n"/>
@@ -14217,7 +14232,7 @@
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="36" t="inlineStr">
         <is>
-          <t>Logística da equipe (deslocamento)</t>
+          <t>Deslocamento da equipe</t>
         </is>
       </c>
       <c r="B97" s="37" t="n"/>
@@ -14277,7 +14292,7 @@
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="36" t="inlineStr">
         <is>
-          <t>Estacionamento, pedágio e outros</t>
+          <t>Estacionamento e pedágio</t>
         </is>
       </c>
       <c r="B99" s="37" t="n"/>
@@ -14658,7 +14673,7 @@
       </c>
       <c r="B120" s="87" t="inlineStr">
         <is>
-          <t>MDF / MDP (chapas)</t>
+          <t>MDF e MDP</t>
         </is>
       </c>
       <c r="C120" s="46" t="n"/>
@@ -14722,7 +14737,7 @@
       </c>
       <c r="B122" s="87" t="inlineStr">
         <is>
-          <t>Consumíveis (parafuso, adesivo, tíner, estopa)</t>
+          <t>Consumíveis</t>
         </is>
       </c>
       <c r="C122" s="46" t="n"/>
@@ -14786,7 +14801,7 @@
       </c>
       <c r="B124" s="87" t="inlineStr">
         <is>
-          <t>Ferragens e acessórios</t>
+          <t>Ferragens</t>
         </is>
       </c>
       <c r="C124" s="46" t="n"/>
@@ -14818,7 +14833,7 @@
       </c>
       <c r="B125" s="87" t="inlineStr">
         <is>
-          <t>Uber / aplicativo</t>
+          <t>Uber e aplicativo</t>
         </is>
       </c>
       <c r="C125" s="46" t="n"/>
@@ -14850,7 +14865,7 @@
       </c>
       <c r="B126" s="87" t="inlineStr">
         <is>
-          <t>MDF / MDP (chapas)</t>
+          <t>MDF e MDP</t>
         </is>
       </c>
       <c r="C126" s="46" t="n"/>
@@ -14914,7 +14929,7 @@
       </c>
       <c r="B128" s="87" t="inlineStr">
         <is>
-          <t>Consumíveis (parafuso, adesivo, tíner, estopa)</t>
+          <t>Consumíveis</t>
         </is>
       </c>
       <c r="C128" s="46" t="n"/>
@@ -14946,7 +14961,7 @@
       </c>
       <c r="B129" s="87" t="inlineStr">
         <is>
-          <t>Ferragens e acessórios</t>
+          <t>Ferragens</t>
         </is>
       </c>
       <c r="C129" s="46" t="n"/>
@@ -14978,7 +14993,7 @@
       </c>
       <c r="B130" s="87" t="inlineStr">
         <is>
-          <t>MDF / MDP (chapas)</t>
+          <t>MDF e MDP</t>
         </is>
       </c>
       <c r="C130" s="46" t="n"/>
@@ -15010,7 +15025,7 @@
       </c>
       <c r="B131" s="87" t="inlineStr">
         <is>
-          <t>Consumíveis (parafuso, adesivo, tíner, estopa)</t>
+          <t>Consumíveis</t>
         </is>
       </c>
       <c r="C131" s="46" t="n"/>
@@ -15138,7 +15153,7 @@
       </c>
       <c r="B135" s="87" t="inlineStr">
         <is>
-          <t>Acabamento (pintura / laca)</t>
+          <t>Acabamento</t>
         </is>
       </c>
       <c r="C135" s="46" t="n"/>
@@ -15170,7 +15185,7 @@
       </c>
       <c r="B136" s="87" t="inlineStr">
         <is>
-          <t>Carreto e frete de entrega</t>
+          <t>Carreto e entrega</t>
         </is>
       </c>
       <c r="C136" s="46" t="n"/>
@@ -15202,7 +15217,7 @@
       </c>
       <c r="B137" s="87" t="inlineStr">
         <is>
-          <t>Uber / aplicativo</t>
+          <t>Uber e aplicativo</t>
         </is>
       </c>
       <c r="C137" s="46" t="n"/>
@@ -15234,7 +15249,7 @@
       </c>
       <c r="B138" s="87" t="inlineStr">
         <is>
-          <t>Carreto e frete de entrega</t>
+          <t>Carreto e entrega</t>
         </is>
       </c>
       <c r="C138" s="46" t="n"/>
@@ -15266,7 +15281,7 @@
       </c>
       <c r="B139" s="87" t="inlineStr">
         <is>
-          <t>Logística da equipe (deslocamento)</t>
+          <t>Deslocamento da equipe</t>
         </is>
       </c>
       <c r="C139" s="46" t="n"/>
@@ -15298,7 +15313,7 @@
       </c>
       <c r="B140" s="87" t="inlineStr">
         <is>
-          <t>Estacionamento, pedágio e outros</t>
+          <t>Estacionamento e pedágio</t>
         </is>
       </c>
       <c r="C140" s="46" t="n"/>
@@ -16369,32 +16384,32 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation sqref="D43:D54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="D43:D54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
-    <dataValidation sqref="G43:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="G43:G54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
-    <dataValidation sqref="A66:A77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="A66:A77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
-    <dataValidation sqref="B104:B115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$C$2:$C$10</formula1>
+    <dataValidation sqref="B104:B115" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=CAUSA_RETRABALHO</formula1>
     </dataValidation>
-    <dataValidation sqref="B120:B179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$D$2:$D$17</formula1>
+    <dataValidation sqref="B120:B179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=CATEGORIA_COMPRA</formula1>
     </dataValidation>
-    <dataValidation sqref="G120:G179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$E$2:$E$9</formula1>
+    <dataValidation sqref="G120:G179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=FORMA_PAGAMENTO</formula1>
     </dataValidation>
-    <dataValidation sqref="I120:I179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$F$2:$F$4</formula1>
+    <dataValidation sqref="I120:I179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=STATUS_COMPRA</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:E7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$B$2:$B$6</formula1>
+    <dataValidation sqref="D7:E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=VENDEDOR</formula1>
     </dataValidation>
-    <dataValidation sqref="F9:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$2:$A$9</formula1>
+    <dataValidation sqref="F9:G9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
+      <formula1>=EQUIPE_COMISSAO</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.3" top="0.4" bottom="0.3" header="0.5" footer="0.5"/>
@@ -16408,7 +16423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16417,7 +16432,8 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16451,7 +16467,12 @@
           <t>Status da compra</t>
         </is>
       </c>
-      <c r="H1" s="93" t="inlineStr">
+      <c r="G1" s="93" t="inlineStr">
+        <is>
+          <t>O que entra nesta categoria</t>
+        </is>
+      </c>
+      <c r="I1" s="93" t="inlineStr">
         <is>
           <t>Para que servem</t>
         </is>
@@ -16475,7 +16496,7 @@
       </c>
       <c r="D2" s="94" t="inlineStr">
         <is>
-          <t>MDF / MDP (chapas)</t>
+          <t>MDF e MDP</t>
         </is>
       </c>
       <c r="E2" s="94" t="inlineStr">
@@ -16488,7 +16509,12 @@
           <t>A comprar</t>
         </is>
       </c>
-      <c r="H2" s="95" t="inlineStr">
+      <c r="G2" s="95" t="inlineStr">
+        <is>
+          <t>chapas cruas e revestidas, por cor e espessura</t>
+        </is>
+      </c>
+      <c r="I2" s="96" t="inlineStr">
         <is>
           <t>Coluna A — só quem recebe comissão: marceneiros, ajudantes e o coordenador. Alimenta produção, montagem, coordenação e o consolidado por colaborador.</t>
         </is>
@@ -16525,7 +16551,12 @@
           <t>Comprado (a pagar)</t>
         </is>
       </c>
-      <c r="H3" s="95" t="inlineStr">
+      <c r="G3" s="95" t="inlineStr">
+        <is>
+          <t>fita de borda de todas as cores e espessuras</t>
+        </is>
+      </c>
+      <c r="I3" s="96" t="inlineStr">
         <is>
           <t>Se acrescentar alguém aqui, inclua também na tabela "Comissões por colaborador" da ficha, senão a pessoa não aparece no consolidado.</t>
         </is>
@@ -16549,7 +16580,7 @@
       </c>
       <c r="D4" s="94" t="inlineStr">
         <is>
-          <t>Ferragens e acessórios</t>
+          <t>Ferragens</t>
         </is>
       </c>
       <c r="E4" s="94" t="inlineStr">
@@ -16562,7 +16593,12 @@
           <t>Pago</t>
         </is>
       </c>
-      <c r="H4" s="95" t="inlineStr">
+      <c r="G4" s="95" t="inlineStr">
+        <is>
+          <t>corrediças, dobradiças, puxadores, pistões, suportes</t>
+        </is>
+      </c>
+      <c r="I4" s="96" t="inlineStr">
         <is>
           <t>Coluna D — as categorias de compra. Se você renomear uma categoria aqui, renomeie também na tabela do bloco 6 da ficha: o SUMIFS casa pelo texto.</t>
         </is>
@@ -16594,7 +16630,12 @@
           <t>Cartão parcelado</t>
         </is>
       </c>
-      <c r="H5" s="95" t="inlineStr">
+      <c r="G5" s="95" t="inlineStr">
+        <is>
+          <t>vidro, espelho e cristal comprados prontos</t>
+        </is>
+      </c>
+      <c r="I5" s="96" t="inlineStr">
         <is>
           <t>Coluna F — status. "A comprar" NÃO entra no custo realizado, entra na coluna "ainda a comprar". "Comprado (a pagar)" e "Pago" entram no custo.</t>
         </is>
@@ -16626,7 +16667,12 @@
           <t>Dinheiro</t>
         </is>
       </c>
-      <c r="H6" s="95" t="inlineStr">
+      <c r="G6" s="95" t="inlineStr">
+        <is>
+          <t>perfis de alumínio, portas de perfil e box</t>
+        </is>
+      </c>
+      <c r="I6" s="96" t="inlineStr">
         <is>
           <t>Coluna C — causas do retrabalho. É a lista mais estratégica da planilha: ela é que vai dizer se o problema está no projeto, na medição, na produção ou no fornecedor.</t>
         </is>
@@ -16653,6 +16699,11 @@
           <t>Transferência</t>
         </is>
       </c>
+      <c r="G7" s="95" t="inlineStr">
+        <is>
+          <t>lâmina de madeira natural e compostos</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="94" t="inlineStr">
@@ -16667,12 +16718,17 @@
       </c>
       <c r="D8" s="94" t="inlineStr">
         <is>
-          <t>Consumíveis (parafuso, adesivo, tíner, estopa)</t>
+          <t>Consumíveis</t>
         </is>
       </c>
       <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Faturado 30 dias</t>
+        </is>
+      </c>
+      <c r="G8" s="95" t="inlineStr">
+        <is>
+          <t>parafuso, adesivo, tíner, estopa, lixa, disco, broca</t>
         </is>
       </c>
     </row>
@@ -16689,12 +16745,17 @@
       </c>
       <c r="D9" s="94" t="inlineStr">
         <is>
-          <t>Acabamento (pintura / laca)</t>
+          <t>Acabamento</t>
         </is>
       </c>
       <c r="E9" s="94" t="inlineStr">
         <is>
           <t>A combinar</t>
+        </is>
+      </c>
+      <c r="G9" s="95" t="inlineStr">
+        <is>
+          <t>pintura, laca, verniz e envernizamento terceirizado</t>
         </is>
       </c>
     </row>
@@ -16709,6 +16770,11 @@
           <t>Serralheria</t>
         </is>
       </c>
+      <c r="G10" s="95" t="inlineStr">
+        <is>
+          <t>estruturas metálicas feitas fora</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="D11" s="94" t="inlineStr">
@@ -16716,6 +16782,11 @@
           <t>Vidraceiro</t>
         </is>
       </c>
+      <c r="G11" s="95" t="inlineStr">
+        <is>
+          <t>corte e instalação de vidro por terceiro</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="D12" s="94" t="inlineStr">
@@ -16723,25 +16794,45 @@
           <t>Outro terceirizado</t>
         </is>
       </c>
+      <c r="G12" s="95" t="inlineStr">
+        <is>
+          <t>qualquer serviço feito fora da fábrica</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="D13" s="94" t="inlineStr">
         <is>
-          <t>Uber / aplicativo</t>
+          <t>Uber e aplicativo</t>
+        </is>
+      </c>
+      <c r="G13" s="95" t="inlineStr">
+        <is>
+          <t>corrida de medição, conferência e visita</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="D14" s="94" t="inlineStr">
         <is>
-          <t>Carreto e frete de entrega</t>
+          <t>Carreto e entrega</t>
+        </is>
+      </c>
+      <c r="G14" s="95" t="inlineStr">
+        <is>
+          <t>transporte do móvel pronto até a obra</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="94" t="inlineStr">
         <is>
-          <t>Logística da equipe (deslocamento)</t>
+          <t>Deslocamento da equipe</t>
+        </is>
+      </c>
+      <c r="G15" s="95" t="inlineStr">
+        <is>
+          <t>ida e volta da equipe de montagem</t>
         </is>
       </c>
     </row>
@@ -16751,11 +16842,21 @@
           <t>Frete de material</t>
         </is>
       </c>
+      <c r="G16" s="95" t="inlineStr">
+        <is>
+          <t>entrega de material do fornecedor até a fábrica</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="D17" s="94" t="inlineStr">
         <is>
-          <t>Estacionamento, pedágio e outros</t>
+          <t>Estacionamento e pedágio</t>
+        </is>
+      </c>
+      <c r="G17" s="95" t="inlineStr">
+        <is>
+          <t>estacionamento, pedágio e miudezas de rota</t>
         </is>
       </c>
     </row>

--- a/painel/planilhas/Valvic_Custo_por_Projeto.xlsx
+++ b/painel/planilhas/Valvic_Custo_por_Projeto.xlsx
@@ -11660,31 +11660,31 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation sqref="D43:D54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
     <dataValidation sqref="G43:G54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
     <dataValidation sqref="A66:A77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
     <dataValidation sqref="B104:B115" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=CAUSA_RETRABALHO</formula1>
+      <formula1>"Erro de projeto,Erro de medição,Erro de produção,Erro de montagem,Falha de material,Dano no transporte,Mudança pedida pelo cliente,Falha de fornecedor,Outro"</formula1>
     </dataValidation>
     <dataValidation sqref="B120:B179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=CATEGORIA_COMPRA</formula1>
+      <formula1>"MDF e MDP,Fita de borda,Ferragens,Vidros e espelhos,Esquadrias,Lâmina natural,Consumíveis,Acabamento,Serralheria,Vidraceiro,Outro terceirizado,Uber e aplicativo,Carreto e entrega,Deslocamento da equipe,Frete de material,Estacionamento e pedágio"</formula1>
     </dataValidation>
     <dataValidation sqref="G120:G179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=FORMA_PAGAMENTO</formula1>
+      <formula1>"PIX,Boleto,Cartão de crédito,Cartão parcelado,Dinheiro,Transferência,Faturado 30 dias,A combinar"</formula1>
     </dataValidation>
     <dataValidation sqref="I120:I179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=STATUS_COMPRA</formula1>
+      <formula1>"A comprar,Comprado (a pagar),Pago"</formula1>
     </dataValidation>
     <dataValidation sqref="D7:E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=VENDEDOR</formula1>
+      <formula1>"Jonathan,Vitor,Indicação,Arquiteto parceiro,Outro"</formula1>
     </dataValidation>
     <dataValidation sqref="F9:G9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.3" top="0.4" bottom="0.3" header="0.5" footer="0.5"/>
@@ -16385,31 +16385,31 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation sqref="D43:D54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
     <dataValidation sqref="G43:G54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
     <dataValidation sqref="A66:A77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
     <dataValidation sqref="B104:B115" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=CAUSA_RETRABALHO</formula1>
+      <formula1>"Erro de projeto,Erro de medição,Erro de produção,Erro de montagem,Falha de material,Dano no transporte,Mudança pedida pelo cliente,Falha de fornecedor,Outro"</formula1>
     </dataValidation>
     <dataValidation sqref="B120:B179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=CATEGORIA_COMPRA</formula1>
+      <formula1>"MDF e MDP,Fita de borda,Ferragens,Vidros e espelhos,Esquadrias,Lâmina natural,Consumíveis,Acabamento,Serralheria,Vidraceiro,Outro terceirizado,Uber e aplicativo,Carreto e entrega,Deslocamento da equipe,Frete de material,Estacionamento e pedágio"</formula1>
     </dataValidation>
     <dataValidation sqref="G120:G179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=FORMA_PAGAMENTO</formula1>
+      <formula1>"PIX,Boleto,Cartão de crédito,Cartão parcelado,Dinheiro,Transferência,Faturado 30 dias,A combinar"</formula1>
     </dataValidation>
     <dataValidation sqref="I120:I179" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=STATUS_COMPRA</formula1>
+      <formula1>"A comprar,Comprado (a pagar),Pago"</formula1>
     </dataValidation>
     <dataValidation sqref="D7:E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=VENDEDOR</formula1>
+      <formula1>"Jonathan,Vitor,Indicação,Arquiteto parceiro,Outro"</formula1>
     </dataValidation>
     <dataValidation sqref="F9:G9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Este valor não está na lista. Você pode manter, mas os totais só somam o que estiver escrito exatamente como na aba Listas." type="list" errorStyle="warning">
-      <formula1>=EQUIPE_COMISSAO</formula1>
+      <formula1>"Deivson,Samuel,Cezar,Jackson,Jomar,Joelson,Jonathan Godoy,Terceiro / avulso"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.3" top="0.4" bottom="0.3" header="0.5" footer="0.5"/>
